--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,29 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:35:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ayan</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>17:12:19</t>
+          <t>10:53:43</t>
         </is>
       </c>
     </row>
